--- a/tarea_2/referencias_plantilla.xlsx
+++ b/tarea_2/referencias_plantilla.xlsx
@@ -347,9 +347,9 @@
 Página 2 de 3</t>
   </si>
   <si>
-    <t>Firmado digitalmente por VALCARCEL SALDANA Juan Julio FAU 20520594451 soft Motivo: Doy V° B° Fecha: 26.05.2026 15:48:47 -05:00
-Firmado digitalmente por MORI KURIYAMA Virgilio Antonio FAU 20520594451 soft Motivo: Doy V° B° Fecha: 26.05.2026 15:53:17 -05:00
-Firmado digitalmente por DE LA FLOR SAENZ Luis Enrique FAU 20520594451 soft Motivo: Doy V° B° Fecha: 26.05.2026 16:15:37 -05:00
+    <t>Firmado digitalmente por [PERSONA_20] FAU 20520594451 soft Motivo: Doy V° B° Fecha: 26.05.2026 15:48:47 -05:00
+Firmado digitalmente por [PERSONA_21] FAU 20520594451 soft Motivo: Doy V° B° Fecha: 26.05.2026 15:53:17 -05:00
+Firmado digitalmente por [PERSONA_22] FAU 20520594451 soft Motivo: Doy V° B° Fecha: 26.05.2026 16:15:37 -05:00
 REPÚBLICA DEL PERÚ
 ético de los sistemas basados en IA del CEPLAN”; asimismo, mediante Acta de Sesión N.° 25, el Comité de Gobierno Digital aprobó la referida propuesta y recomendó su formalización mediante Resolución de Presidencia del Consejo Directivo, por encontrarse alineada con el marco normativo vigente y los objetivos institucionales del CEPLAN;
 Con el visado del Director Ejecutivo, del Jefe de la Oficina de Planeamiento y Presupuesto y del Jefe de la Oficina de Asesoría Jurídica del Centro Nacional de Planeamiento Estratégico CEPLAN; y,
@@ -360,21 +360,21 @@
 Artículo 3.- DIFUNDIR la presente Resolución a los servidores de la entidad.
 Artículo 4.- DISPONER que la Oficina General de Administración realice las gestiones para la publicación de la presente Resolución y su anexo, en el portal institucional del Centro Nacional de Planeamiento Estratégico (www.gob.pe/ceplan).
 Regístrese y comuníquese.
-Firmado digitalmente por PEIRANO TORRIANI Giofianni Diglio FAU 20520594451 soft Motivo: Soy el autor del documento Fecha: 26.05.2026 17:12:35 -05:00
-GIOFIANNI DIGLIO PEIRANO TORRIANI
+Firmado digitalmente por [PERSONA_23] FAU 20520594451 soft Motivo: Soy el autor del documento Fecha: 26.05.2026 17:12:35 -05:00
+[PERSONA_23]
 Presidente del Consejo Directivo del CEPLAN
 Página 2 de 2</t>
   </si>
   <si>
-    <t>Firmado digitalmente por VALCARCEL SALDANA Juan Julio FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 10:39:02 -05:00
-Firmado digitalmente por RIVADENEIRA SANTA MARIA Amaro Angel FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 10:40:54 -05:00
-Firmado digitalmente por ATAUCUSI ATAUCUSI Yirem Amaro FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 11:24:09 -05:00
-Firmado digitalmente por DE LA FLOR SAENZ Luis Enrique FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 11:56:13 -05:00
+    <t>Firmado digitalmente por [PERSONA_20] FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 10:39:02 -05:00
+Firmado digitalmente por [PERSONA_24] FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 10:40:54 -05:00
+Firmado digitalmente por [PERSONA_25] FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 11:24:09 -05:00
+Firmado digitalmente por [PERSONA_22] FAU 20520594451 soft Motivo: Doy V° B° Fecha: 27.08.2025 11:56:13 -05:00
 REPÚBLICA DEL PERÚ
 El Peruano, así como de la actualización del Plan Estratégico de Desarrollo Nacional, en el Portal Institucional del Centro Nacional de Planeamiento Estratégico www.gob.pe/ceplan .
 Regístrese, comuníquese y publíquese.
-Firmado digitalmente por PEIRANO TORRIANI Giofianni Diglio FAU 20520594451 soft Motivo: Soy el autor del documento Fecha: 27.08.2025 12:34:01 -05:00
-GIOFIANNI DIGLIO PEIRANO TORRIANI
+Firmado digitalmente por [PERSONA_23] FAU 20520594451 soft Motivo: Soy el autor del documento Fecha: 27.08.2025 12:34:01 -05:00
+[PERSONA_23]
 Presidente del Consejo Directivo del CEPLAN
 Página 2 de 2</t>
   </si>
@@ -382,13 +382,13 @@
     <t>¿Cómo te sientes cuando hay partidos de Perú? Contenta, porque va a ganar Perú. ¿Y si, y si no gana Perú? ¿Y si no gana Perú? Pues me pongo triste.</t>
   </si>
   <si>
-    <t>Normal, esperando resultados nomás. Pero ¿cómo lo ves? ¿Cómo ves a Perú ahorita que está...? ¿Cómo le veo a Perú? Perú le veo hasta las... Está... no se, no se, no se entienden, pe. No se están entendiendo. No, no, hay como cuatro jugadores que están por las puras y ya, pe, ahora el técnico tiene que hacer justo los cambios, pe, ¿no? Supongo esos cuatro jugadores, que es Carrillo, Canchita, este, Trauco y... y... ah, el otro sí no...</t>
-  </si>
-  <si>
-    <t>Buenas noches, soy Jean Pierre Venegas, estudiante de la San Marcos. Esta entrevista va a ser registrada en internet. ¿Está de acuerdo usted? Sí, estoy de acuerdo. Muy bien. Para usted, ¿qué es el Perú? Pues yo no soy peruano, de entrada. Pero Perú, yo creo que junto con México, los dos países que más historia tienen, más cultura y más restos de civilizaciones prehispánicas, más ciudades coloniales, mucho más riqueza de folclor, de todo. En América me parece que son los dos más ricos. Muchas gracias. Y usted, en su estadía en Perú, ¿cuáles son las principales características positivas que podría destacar de...? La gente es increíblemente amable. Lima, por ejemplo, me parece una ciudad muy ordenada, muy limpia, la tienen muy bien organizada. Llevo apenas un día, entonces no te puedo decir mucho más de eso. Y en ese día, ¿cuál sería el aspecto más negativo que notó? Pues aquí en Lima el servicio es muy lento. El servicio es terriblemente lento en los restaurantes. Pero digo, eso no es que sea tan negativo, es lo único negativo que te puedo decir de Lima en realidad. Ya, muchas gracias, señor. Felices fiestas.</t>
-  </si>
-  <si>
-    <t>Ese día estaba haciendo prácticas y me tocó hacer guardia. Cuando llegó una paciente a la sala de expulsivos y salió una obstetra a la que la llamaban la Triki, y prácticamente jaló a la paciente a una sala que ellos usaban para atender partos. Ahí empezó a gritarle a la paciente y nosotras escuchábamos: "Abre las piernas, mierda. Para hacer hijos sí eres buena. Jódete, mierda. Así es el parto, pues". Y vimos que le hincaba o picaba con el lapicero en las piernas, hasta que la paciente se paró y salió de esa sala. Otras obstetras la socorrieron mientras la Triki le gritaba: "Te vas a morir, mierda, y por tu culpa tu hijo también se va a morir".</t>
+    <t>Normal, esperando resultados nomás. Pero ¿cómo lo ves? ¿Cómo ves a Perú ahorita que está...? ¿Cómo le veo a Perú? Perú le veo hasta las... Está... no se, no se, no se entienden, pe. No se están entendiendo. No, no, hay como cuatro jugadores que están por las puras y ya, pe, ahora el técnico tiene que hacer justo los cambios, pe, ¿no? Supongo esos cuatro jugadores, que es [PERSONA_42], [PERSONA_43], este, [PERSONA_44] y... y... ah, el otro sí no...</t>
+  </si>
+  <si>
+    <t>Buenas noches, soy [PERSONA_6], estudiante de la San Marcos. Esta entrevista va a ser registrada en internet. ¿Está de acuerdo usted? Sí, estoy de acuerdo. Muy bien. Para usted, ¿qué es el Perú? Pues yo no soy peruano, de entrada. Pero Perú, yo creo que junto con México, los dos países que más historia tienen, más cultura y más restos de civilizaciones prehispánicas, más ciudades coloniales, mucho más riqueza de folclor, de todo. En América me parece que son los dos más ricos. Muchas gracias. Y usted, en su estadía en Perú, ¿cuáles son las principales características positivas que podría destacar de...? La gente es increíblemente amable. Lima, por ejemplo, me parece una ciudad muy ordenada, muy limpia, la tienen muy bien organizada. Llevo apenas un día, entonces no te puedo decir mucho más de eso. Y en ese día, ¿cuál sería el aspecto más negativo que notó? Pues aquí en Lima el servicio es muy lento. El servicio es terriblemente lento en los restaurantes. Pero digo, eso no es que sea tan negativo, es lo único negativo que te puedo decir de Lima en realidad. Ya, muchas gracias, señor. Felices fiestas.</t>
+  </si>
+  <si>
+    <t>Ese día estaba haciendo prácticas y me tocó hacer guardia. Cuando llegó una paciente a la sala de expulsivos y salió una obstetra a la que la llamaban [PERSONA_11], y prácticamente jaló a la paciente a una sala que ellos usaban para atender partos. Ahí empezó a gritarle a la paciente y nosotras escuchábamos: "Abre las piernas, mierda. Para hacer hijos sí eres buena. Jódete, mierda. Así es el parto, pues". Y vimos que le hincaba o picaba con el lapicero en las piernas, hasta que la paciente se paró y salió de esa sala. Otras obstetras la socorrieron mientras [PERSONA_11] le gritaba: "Te vas a morir, mierda, y por tu culpa tu hijo también se va a morir".</t>
   </si>
   <si>
     <t>Soy psicóloga comunitaria de un C en Cajamarca. Una de las usuarias me comentó que tenía cinco meses de embarazo y que no fue a hacerse su chequeo porque temía ser criticada por las obstetras. Fui a hablar con las obstetras para saber si conocían a la usuaria y solicitarles que le hagan el seguimiento. Antes de que pueda terminar de exponer el caso, una de las obstetras comentó: "¿Esa señora otra vez está embarazada? ¿Cómo para tener hijos es buena, pero ni viene a hacerse sus controles? Ya le dije, ya, es su sexto hijo. ¿Hasta cuándo ya?" Entendí por qué la usuaria no se había atrevido a asistir a sus controles.</t>
@@ -403,10 +403,10 @@
     <t>Por nuestras muertas y desaparecidas, ni un minuto de silencio, toda una vida de lucha. Por nuestras muertas y desaparecidas, ni un minuto de silencio, toda una vida de lucha. Por nuestras muertas y desaparecidas, ni un minuto de silencio, toda una vida de lucha. ¿Qué exigimos las mujeres? Justicia. ¿Qué exigimos las mujeres? Justicia. ¿Cuándo? Ahora. ¿Cuándo? Ahora. ¿Qué exigimos las madres? Justicia. ¿Qué exigimos las madres? Justicia. ¿Qué exigimos las madres? Justicia. ¿Cuándo? Ahora. ¿Cuándo? Ahora. Justicia que tarda no es justicia. Justicia que tarda no es justicia.</t>
   </si>
   <si>
-    <t>Bueno, ahora estamos en Plaza San Martín, entre Fiestas Patrias, ¿no? 28 de julio. Entonces, primero, ¿podría comenzar diciéndome su nombre, por favor? Mi nombre es Aurora Coronado. Aurora Coronado, bien. Primera pregunta para usted. Para usted, ¿qué significa el Perú? Bueno, el Perú es mi país donde he nacido, amo mucho porque acá vivo, tengo todo lo que necesito y adoro mi país. Es mi patria, es un territorio donde nosotros vivimos, ¿no? Por ejemplo, yo soy de la selva central. Amo mi territorio porque de ahí vivo, de ahí como, tengo mi medicina, mis plantas ancestrales, tengo mi cultura y mi identidad también. Y usted, ¿en qué momento diría usted que se dio cuenta de que era peruana, que sintió que era peruana? Bueno, creo que desde que he nacido siempre, ¿no? Nuestros padres nos han inculcado que siempre el 28 de julio, el día de la independencia, ¿no? Desde muy pequeños lo celebrábamos, ¿no? No solamente con alimentación, sino que era nuestro Perú y que nos compraban ropa nueva. Me acuerdo de pequeños, una fiesta, era una fiesta para nosotros, ¿no? Yo creo que eso se ha perdido un poco, la tradición, porque algunos nos compraban hasta juguetes también. Era como Navidad, sí, 28 de julio, y nos compraban ropa, ¿no? Era, uy, era la fiesta y que íbamos a los desfiles, ¿no? En nuestra zona donde vivimos, ¿no? Muy bonito, pero creo que eso se ha perdido un poco. Y ahora, ¿cuál diría que son los aspectos positivos, las características positivas del Perú?</t>
-  </si>
-  <si>
-    <t>Mi nombre es Lucinda Quispialaya Salvatierra. ¿De dónde vienes y de qué, cuál es tu comunidad? Yo vengo de la comunidad campesina de Chicuy, del distrito San Juan de Jarpa de la provincia de Chupaca. Bien, como ustedes saben, yo vengo trabajando desde muy niña en la chacra, conjuntamente con mis padres, donde también me enseñaron la responsabilidad. Con el ejemplo me enseñaron a trabajar con dignidad en la agricultura. Somos de la pequeña agricultura, en donde producimos lo que es habas, papas, cebada y otros. Nos dedicamos también a la agricultura, a la ganadería. Todos son de autoconsumo los alimentos, porque nosotros nos encontramos entre los 3800 sobre el nivel del mar. Pero sin embargo, desde el año 2000, 2000, nosotros veníamos promoviendo toda la agricultura sostenible, en las cuales la agricultura sostenible, donde vemos la parte social, vemos la parte política, la parte cultural. Y entonces, en esas dimensiones de verdad que nosotros hemos hecho, trabajado bastante en las provincias de Concepción, Chupaca y Huancayo, y todo relacionado a lo que es basado a la agroecología con alimentos sanos, y eso garantiza la alimentación del Perú y también del mundo. La alimentación es la base fundamental y somos el 93 por ciento de productores de la pequeña agricultura que nosotros subsistimos a los mercados locales, a los mercados nacionales, y así estamos subsistiendo esa gran alimentación que nosotros lo tenemos.</t>
+    <t>Bueno, ahora estamos en Plaza San Martín, entre Fiestas Patrias, ¿no? 28 de julio. Entonces, primero, ¿podría comenzar diciéndome su nombre, por favor? Mi nombre es [PERSONA_4]. [PERSONA_4], bien. Primera pregunta para usted. Para usted, ¿qué significa el Perú? Bueno, el Perú es mi país donde he nacido, amo mucho porque acá vivo, tengo todo lo que necesito y adoro mi país. Es mi patria, es un territorio donde nosotros vivimos, ¿no? Por ejemplo, yo soy de la selva central. Amo mi territorio porque de ahí vivo, de ahí como, tengo mi medicina, mis plantas ancestrales, tengo mi cultura y mi identidad también. Y usted, ¿en qué momento diría usted que se dio cuenta de que era peruana, que sintió que era peruana? Bueno, creo que desde que he nacido siempre, ¿no? Nuestros padres nos han inculcado que siempre el 28 de julio, el día de la independencia, ¿no? Desde muy pequeños lo celebrábamos, ¿no? No solamente con alimentación, sino que era nuestro Perú y que nos compraban ropa nueva. Me acuerdo de pequeños, una fiesta, era una fiesta para nosotros, ¿no? Yo creo que eso se ha perdido un poco, la tradición, porque algunos nos compraban hasta juguetes también. Era como Navidad, sí, 28 de julio, y nos compraban ropa, ¿no? Era, uy, era la fiesta y que íbamos a los desfiles, ¿no? En nuestra zona donde vivimos, ¿no? Muy bonito, pero creo que eso se ha perdido un poco. Y ahora, ¿cuál diría que son los aspectos positivos, las características positivas del Perú?</t>
+  </si>
+  <si>
+    <t>Mi nombre es [PERSONA_5]. ¿De dónde vienes y de qué, cuál es tu comunidad? Yo vengo de la comunidad campesina de Chicuy, del distrito San Juan de Jarpa de la provincia de Chupaca. Bien, como ustedes saben, yo vengo trabajando desde muy niña en la chacra, conjuntamente con mis padres, donde también me enseñaron la responsabilidad. Con el ejemplo me enseñaron a trabajar con dignidad en la agricultura. Somos de la pequeña agricultura, en donde producimos lo que es habas, papas, cebada y otros. Nos dedicamos también a la agricultura, a la ganadería. Todos son de autoconsumo los alimentos, porque nosotros nos encontramos entre los 3800 sobre el nivel del mar. Pero sin embargo, desde el año 2000, 2000, nosotros veníamos promoviendo toda la agricultura sostenible, en las cuales la agricultura sostenible, donde vemos la parte social, vemos la parte política, la parte cultural. Y entonces, en esas dimensiones de verdad que nosotros hemos hecho, trabajado bastante en las provincias de Concepción, Chupaca y Huancayo, y todo relacionado a lo que es basado a la agroecología con alimentos sanos, y eso garantiza la alimentación del Perú y también del mundo. La alimentación es la base fundamental y somos el 93 por ciento de productores de la pequeña agricultura que nosotros subsistimos a los mercados locales, a los mercados nacionales, y así estamos subsistiendo esa gran alimentación que nosotros lo tenemos.</t>
   </si>
 </sst>
 </file>
